--- a/Data/EC/NIT-9008979710.xlsx
+++ b/Data/EC/NIT-9008979710.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98F18F8D-D538-4338-ABF3-D3A2558B2602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFD32265-4301-42D8-947B-098234F6C3BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{216F1F05-0CF3-4DE2-A4A7-7893A3926648}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{A75400A7-9BAB-44D2-B77C-D24FD6967C2A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -689,22 +689,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEB2D4DD-5CF5-D8F5-D906-AA35B1BFE3A3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE51CC7D-877E-8120-354C-4D9F9234D782}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -713,7 +713,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -726,7 +726,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1055,23 +1055,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{185C4A3E-A23C-4D0C-89BB-C48A04BAE994}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29879316-8EF8-4CE2-BA44-DEB7BF01037D}">
   <dimension ref="B2:J289"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1084,7 +1084,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1095,7 +1095,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1106,7 +1106,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1117,8 +1117,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>85</v>
       </c>
@@ -1133,8 +1133,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1149,8 +1149,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>86</v>
       </c>
@@ -1165,8 +1165,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>87</v>
       </c>
@@ -1185,7 +1185,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1237,7 +1237,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1260,7 +1260,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +1283,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1306,7 +1306,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1329,7 +1329,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1352,7 +1352,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1375,7 +1375,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1398,7 +1398,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1421,7 +1421,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1490,7 +1490,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1513,7 +1513,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1536,7 +1536,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1582,7 +1582,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1605,7 +1605,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1628,7 +1628,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1651,7 +1651,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1674,7 +1674,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1720,7 +1720,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1743,7 +1743,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1766,7 +1766,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1789,7 +1789,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1812,7 +1812,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1835,7 +1835,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1858,7 +1858,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1881,7 +1881,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1927,7 +1927,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1950,7 +1950,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1973,7 +1973,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1996,7 +1996,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2019,7 +2019,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2042,7 +2042,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2065,7 +2065,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2088,7 +2088,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2111,7 +2111,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2134,7 +2134,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2157,7 +2157,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2180,7 +2180,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2203,7 +2203,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2226,7 +2226,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2272,7 +2272,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2295,7 +2295,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2318,7 +2318,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2341,7 +2341,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2364,7 +2364,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2387,7 +2387,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2410,7 +2410,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2433,7 +2433,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2456,7 +2456,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2479,7 +2479,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2502,7 +2502,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2548,7 +2548,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2571,7 +2571,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2594,7 +2594,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2617,7 +2617,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2640,7 +2640,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2663,7 +2663,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2686,7 +2686,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2709,7 +2709,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2732,7 +2732,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2755,7 +2755,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2778,7 +2778,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2824,7 +2824,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2847,7 +2847,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2870,7 +2870,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2893,7 +2893,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2916,7 +2916,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2939,7 +2939,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2962,7 +2962,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2985,7 +2985,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3008,7 +3008,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -3031,7 +3031,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -3054,7 +3054,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -3077,7 +3077,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -3100,7 +3100,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3123,7 +3123,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3146,7 +3146,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3169,7 +3169,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3192,7 +3192,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3215,7 +3215,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3238,7 +3238,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3261,7 +3261,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3284,7 +3284,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3307,7 +3307,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3330,7 +3330,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3376,7 +3376,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3399,7 +3399,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3422,7 +3422,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3445,7 +3445,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3468,7 +3468,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3491,7 +3491,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3514,7 +3514,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3537,7 +3537,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3560,7 +3560,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3583,7 +3583,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3606,7 +3606,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3629,7 +3629,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3652,7 +3652,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3675,7 +3675,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3698,7 +3698,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3721,7 +3721,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3744,7 +3744,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3767,7 +3767,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3790,7 +3790,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3813,7 +3813,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3836,7 +3836,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3859,7 +3859,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3882,7 +3882,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3905,7 +3905,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3928,7 +3928,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3951,7 +3951,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3974,7 +3974,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3997,7 +3997,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -4020,7 +4020,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -4043,7 +4043,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -4066,7 +4066,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -4089,7 +4089,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4112,7 +4112,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="15" t="s">
         <v>8</v>
       </c>
@@ -4158,7 +4158,7 @@
       <c r="I143" s="19"/>
       <c r="J143" s="20"/>
     </row>
-    <row r="144" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B144" s="15" t="s">
         <v>8</v>
       </c>
@@ -4181,7 +4181,7 @@
       <c r="I144" s="19"/>
       <c r="J144" s="20"/>
     </row>
-    <row r="145" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B145" s="15" t="s">
         <v>8</v>
       </c>
@@ -4204,7 +4204,7 @@
       <c r="I145" s="19"/>
       <c r="J145" s="20"/>
     </row>
-    <row r="146" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B146" s="15" t="s">
         <v>8</v>
       </c>
@@ -4227,7 +4227,7 @@
       <c r="I146" s="19"/>
       <c r="J146" s="20"/>
     </row>
-    <row r="147" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B147" s="15" t="s">
         <v>8</v>
       </c>
@@ -4250,7 +4250,7 @@
       <c r="I147" s="19"/>
       <c r="J147" s="20"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="15" t="s">
         <v>8</v>
       </c>
@@ -4273,7 +4273,7 @@
       <c r="I148" s="19"/>
       <c r="J148" s="20"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="15" t="s">
         <v>8</v>
       </c>
@@ -4296,7 +4296,7 @@
       <c r="I149" s="19"/>
       <c r="J149" s="20"/>
     </row>
-    <row r="150" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B150" s="15" t="s">
         <v>8</v>
       </c>
@@ -4319,7 +4319,7 @@
       <c r="I150" s="19"/>
       <c r="J150" s="20"/>
     </row>
-    <row r="151" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B151" s="15" t="s">
         <v>8</v>
       </c>
@@ -4342,7 +4342,7 @@
       <c r="I151" s="19"/>
       <c r="J151" s="20"/>
     </row>
-    <row r="152" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B152" s="15" t="s">
         <v>8</v>
       </c>
@@ -4365,7 +4365,7 @@
       <c r="I152" s="19"/>
       <c r="J152" s="20"/>
     </row>
-    <row r="153" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B153" s="15" t="s">
         <v>8</v>
       </c>
@@ -4388,7 +4388,7 @@
       <c r="I153" s="19"/>
       <c r="J153" s="20"/>
     </row>
-    <row r="154" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B154" s="15" t="s">
         <v>8</v>
       </c>
@@ -4411,7 +4411,7 @@
       <c r="I154" s="19"/>
       <c r="J154" s="20"/>
     </row>
-    <row r="155" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B155" s="15" t="s">
         <v>8</v>
       </c>
@@ -4434,7 +4434,7 @@
       <c r="I155" s="19"/>
       <c r="J155" s="20"/>
     </row>
-    <row r="156" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B156" s="15" t="s">
         <v>8</v>
       </c>
@@ -4457,7 +4457,7 @@
       <c r="I156" s="19"/>
       <c r="J156" s="20"/>
     </row>
-    <row r="157" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B157" s="15" t="s">
         <v>8</v>
       </c>
@@ -4480,7 +4480,7 @@
       <c r="I157" s="19"/>
       <c r="J157" s="20"/>
     </row>
-    <row r="158" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B158" s="15" t="s">
         <v>8</v>
       </c>
@@ -4503,7 +4503,7 @@
       <c r="I158" s="19"/>
       <c r="J158" s="20"/>
     </row>
-    <row r="159" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B159" s="15" t="s">
         <v>8</v>
       </c>
@@ -4526,7 +4526,7 @@
       <c r="I159" s="19"/>
       <c r="J159" s="20"/>
     </row>
-    <row r="160" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B160" s="15" t="s">
         <v>8</v>
       </c>
@@ -4549,7 +4549,7 @@
       <c r="I160" s="19"/>
       <c r="J160" s="20"/>
     </row>
-    <row r="161" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B161" s="15" t="s">
         <v>8</v>
       </c>
@@ -4572,7 +4572,7 @@
       <c r="I161" s="19"/>
       <c r="J161" s="20"/>
     </row>
-    <row r="162" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B162" s="15" t="s">
         <v>8</v>
       </c>
@@ -4595,7 +4595,7 @@
       <c r="I162" s="19"/>
       <c r="J162" s="20"/>
     </row>
-    <row r="163" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B163" s="15" t="s">
         <v>8</v>
       </c>
@@ -4618,7 +4618,7 @@
       <c r="I163" s="19"/>
       <c r="J163" s="20"/>
     </row>
-    <row r="164" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B164" s="15" t="s">
         <v>8</v>
       </c>
@@ -4641,7 +4641,7 @@
       <c r="I164" s="19"/>
       <c r="J164" s="20"/>
     </row>
-    <row r="165" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B165" s="15" t="s">
         <v>8</v>
       </c>
@@ -4664,7 +4664,7 @@
       <c r="I165" s="19"/>
       <c r="J165" s="20"/>
     </row>
-    <row r="166" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B166" s="15" t="s">
         <v>8</v>
       </c>
@@ -4687,7 +4687,7 @@
       <c r="I166" s="19"/>
       <c r="J166" s="20"/>
     </row>
-    <row r="167" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B167" s="15" t="s">
         <v>8</v>
       </c>
@@ -4710,7 +4710,7 @@
       <c r="I167" s="19"/>
       <c r="J167" s="20"/>
     </row>
-    <row r="168" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B168" s="15" t="s">
         <v>8</v>
       </c>
@@ -4733,7 +4733,7 @@
       <c r="I168" s="19"/>
       <c r="J168" s="20"/>
     </row>
-    <row r="169" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B169" s="15" t="s">
         <v>8</v>
       </c>
@@ -4756,7 +4756,7 @@
       <c r="I169" s="19"/>
       <c r="J169" s="20"/>
     </row>
-    <row r="170" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B170" s="15" t="s">
         <v>8</v>
       </c>
@@ -4779,7 +4779,7 @@
       <c r="I170" s="19"/>
       <c r="J170" s="20"/>
     </row>
-    <row r="171" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B171" s="15" t="s">
         <v>8</v>
       </c>
@@ -4802,7 +4802,7 @@
       <c r="I171" s="19"/>
       <c r="J171" s="20"/>
     </row>
-    <row r="172" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B172" s="15" t="s">
         <v>8</v>
       </c>
@@ -4825,7 +4825,7 @@
       <c r="I172" s="19"/>
       <c r="J172" s="20"/>
     </row>
-    <row r="173" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B173" s="15" t="s">
         <v>8</v>
       </c>
@@ -4848,7 +4848,7 @@
       <c r="I173" s="19"/>
       <c r="J173" s="20"/>
     </row>
-    <row r="174" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B174" s="15" t="s">
         <v>8</v>
       </c>
@@ -4871,7 +4871,7 @@
       <c r="I174" s="19"/>
       <c r="J174" s="20"/>
     </row>
-    <row r="175" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B175" s="15" t="s">
         <v>8</v>
       </c>
@@ -4894,7 +4894,7 @@
       <c r="I175" s="19"/>
       <c r="J175" s="20"/>
     </row>
-    <row r="176" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B176" s="15" t="s">
         <v>8</v>
       </c>
@@ -4917,7 +4917,7 @@
       <c r="I176" s="19"/>
       <c r="J176" s="20"/>
     </row>
-    <row r="177" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B177" s="15" t="s">
         <v>8</v>
       </c>
@@ -4940,7 +4940,7 @@
       <c r="I177" s="19"/>
       <c r="J177" s="20"/>
     </row>
-    <row r="178" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B178" s="15" t="s">
         <v>8</v>
       </c>
@@ -4963,7 +4963,7 @@
       <c r="I178" s="19"/>
       <c r="J178" s="20"/>
     </row>
-    <row r="179" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B179" s="15" t="s">
         <v>8</v>
       </c>
@@ -4986,7 +4986,7 @@
       <c r="I179" s="19"/>
       <c r="J179" s="20"/>
     </row>
-    <row r="180" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B180" s="15" t="s">
         <v>8</v>
       </c>
@@ -5009,7 +5009,7 @@
       <c r="I180" s="19"/>
       <c r="J180" s="20"/>
     </row>
-    <row r="181" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B181" s="15" t="s">
         <v>8</v>
       </c>
@@ -5032,7 +5032,7 @@
       <c r="I181" s="19"/>
       <c r="J181" s="20"/>
     </row>
-    <row r="182" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B182" s="15" t="s">
         <v>8</v>
       </c>
@@ -5055,7 +5055,7 @@
       <c r="I182" s="19"/>
       <c r="J182" s="20"/>
     </row>
-    <row r="183" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B183" s="15" t="s">
         <v>8</v>
       </c>
@@ -5078,7 +5078,7 @@
       <c r="I183" s="19"/>
       <c r="J183" s="20"/>
     </row>
-    <row r="184" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B184" s="15" t="s">
         <v>8</v>
       </c>
@@ -5101,7 +5101,7 @@
       <c r="I184" s="19"/>
       <c r="J184" s="20"/>
     </row>
-    <row r="185" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B185" s="15" t="s">
         <v>8</v>
       </c>
@@ -5124,7 +5124,7 @@
       <c r="I185" s="19"/>
       <c r="J185" s="20"/>
     </row>
-    <row r="186" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B186" s="15" t="s">
         <v>8</v>
       </c>
@@ -5147,7 +5147,7 @@
       <c r="I186" s="19"/>
       <c r="J186" s="20"/>
     </row>
-    <row r="187" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B187" s="15" t="s">
         <v>8</v>
       </c>
@@ -5170,7 +5170,7 @@
       <c r="I187" s="19"/>
       <c r="J187" s="20"/>
     </row>
-    <row r="188" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B188" s="15" t="s">
         <v>8</v>
       </c>
@@ -5193,7 +5193,7 @@
       <c r="I188" s="19"/>
       <c r="J188" s="20"/>
     </row>
-    <row r="189" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B189" s="15" t="s">
         <v>8</v>
       </c>
@@ -5216,7 +5216,7 @@
       <c r="I189" s="19"/>
       <c r="J189" s="20"/>
     </row>
-    <row r="190" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B190" s="15" t="s">
         <v>8</v>
       </c>
@@ -5239,7 +5239,7 @@
       <c r="I190" s="19"/>
       <c r="J190" s="20"/>
     </row>
-    <row r="191" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B191" s="15" t="s">
         <v>8</v>
       </c>
@@ -5262,7 +5262,7 @@
       <c r="I191" s="19"/>
       <c r="J191" s="20"/>
     </row>
-    <row r="192" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B192" s="15" t="s">
         <v>8</v>
       </c>
@@ -5285,7 +5285,7 @@
       <c r="I192" s="19"/>
       <c r="J192" s="20"/>
     </row>
-    <row r="193" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B193" s="15" t="s">
         <v>8</v>
       </c>
@@ -5308,7 +5308,7 @@
       <c r="I193" s="19"/>
       <c r="J193" s="20"/>
     </row>
-    <row r="194" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B194" s="15" t="s">
         <v>8</v>
       </c>
@@ -5331,7 +5331,7 @@
       <c r="I194" s="19"/>
       <c r="J194" s="20"/>
     </row>
-    <row r="195" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B195" s="15" t="s">
         <v>8</v>
       </c>
@@ -5354,7 +5354,7 @@
       <c r="I195" s="19"/>
       <c r="J195" s="20"/>
     </row>
-    <row r="196" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B196" s="15" t="s">
         <v>8</v>
       </c>
@@ -5377,7 +5377,7 @@
       <c r="I196" s="19"/>
       <c r="J196" s="20"/>
     </row>
-    <row r="197" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B197" s="15" t="s">
         <v>8</v>
       </c>
@@ -5400,7 +5400,7 @@
       <c r="I197" s="19"/>
       <c r="J197" s="20"/>
     </row>
-    <row r="198" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B198" s="15" t="s">
         <v>8</v>
       </c>
@@ -5423,7 +5423,7 @@
       <c r="I198" s="19"/>
       <c r="J198" s="20"/>
     </row>
-    <row r="199" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B199" s="15" t="s">
         <v>8</v>
       </c>
@@ -5446,7 +5446,7 @@
       <c r="I199" s="19"/>
       <c r="J199" s="20"/>
     </row>
-    <row r="200" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B200" s="15" t="s">
         <v>8</v>
       </c>
@@ -5469,7 +5469,7 @@
       <c r="I200" s="19"/>
       <c r="J200" s="20"/>
     </row>
-    <row r="201" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B201" s="15" t="s">
         <v>8</v>
       </c>
@@ -5492,7 +5492,7 @@
       <c r="I201" s="19"/>
       <c r="J201" s="20"/>
     </row>
-    <row r="202" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B202" s="15" t="s">
         <v>8</v>
       </c>
@@ -5515,7 +5515,7 @@
       <c r="I202" s="19"/>
       <c r="J202" s="20"/>
     </row>
-    <row r="203" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B203" s="15" t="s">
         <v>8</v>
       </c>
@@ -5538,7 +5538,7 @@
       <c r="I203" s="19"/>
       <c r="J203" s="20"/>
     </row>
-    <row r="204" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B204" s="15" t="s">
         <v>8</v>
       </c>
@@ -5561,7 +5561,7 @@
       <c r="I204" s="19"/>
       <c r="J204" s="20"/>
     </row>
-    <row r="205" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B205" s="15" t="s">
         <v>8</v>
       </c>
@@ -5584,7 +5584,7 @@
       <c r="I205" s="19"/>
       <c r="J205" s="20"/>
     </row>
-    <row r="206" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B206" s="15" t="s">
         <v>8</v>
       </c>
@@ -5607,7 +5607,7 @@
       <c r="I206" s="19"/>
       <c r="J206" s="20"/>
     </row>
-    <row r="207" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B207" s="15" t="s">
         <v>8</v>
       </c>
@@ -5630,7 +5630,7 @@
       <c r="I207" s="19"/>
       <c r="J207" s="20"/>
     </row>
-    <row r="208" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B208" s="15" t="s">
         <v>8</v>
       </c>
@@ -5653,7 +5653,7 @@
       <c r="I208" s="19"/>
       <c r="J208" s="20"/>
     </row>
-    <row r="209" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B209" s="15" t="s">
         <v>8</v>
       </c>
@@ -5676,7 +5676,7 @@
       <c r="I209" s="19"/>
       <c r="J209" s="20"/>
     </row>
-    <row r="210" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B210" s="15" t="s">
         <v>8</v>
       </c>
@@ -5699,7 +5699,7 @@
       <c r="I210" s="19"/>
       <c r="J210" s="20"/>
     </row>
-    <row r="211" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B211" s="15" t="s">
         <v>8</v>
       </c>
@@ -5722,7 +5722,7 @@
       <c r="I211" s="19"/>
       <c r="J211" s="20"/>
     </row>
-    <row r="212" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B212" s="15" t="s">
         <v>8</v>
       </c>
@@ -5745,7 +5745,7 @@
       <c r="I212" s="19"/>
       <c r="J212" s="20"/>
     </row>
-    <row r="213" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B213" s="15" t="s">
         <v>8</v>
       </c>
@@ -5768,7 +5768,7 @@
       <c r="I213" s="19"/>
       <c r="J213" s="20"/>
     </row>
-    <row r="214" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="214" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B214" s="15" t="s">
         <v>8</v>
       </c>
@@ -5791,7 +5791,7 @@
       <c r="I214" s="19"/>
       <c r="J214" s="20"/>
     </row>
-    <row r="215" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="215" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B215" s="15" t="s">
         <v>8</v>
       </c>
@@ -5814,7 +5814,7 @@
       <c r="I215" s="19"/>
       <c r="J215" s="20"/>
     </row>
-    <row r="216" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="216" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B216" s="15" t="s">
         <v>8</v>
       </c>
@@ -5837,7 +5837,7 @@
       <c r="I216" s="19"/>
       <c r="J216" s="20"/>
     </row>
-    <row r="217" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="217" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B217" s="15" t="s">
         <v>8</v>
       </c>
@@ -5860,7 +5860,7 @@
       <c r="I217" s="19"/>
       <c r="J217" s="20"/>
     </row>
-    <row r="218" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="218" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B218" s="15" t="s">
         <v>8</v>
       </c>
@@ -5883,7 +5883,7 @@
       <c r="I218" s="19"/>
       <c r="J218" s="20"/>
     </row>
-    <row r="219" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="219" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B219" s="15" t="s">
         <v>8</v>
       </c>
@@ -5906,7 +5906,7 @@
       <c r="I219" s="19"/>
       <c r="J219" s="20"/>
     </row>
-    <row r="220" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="220" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B220" s="15" t="s">
         <v>8</v>
       </c>
@@ -5929,7 +5929,7 @@
       <c r="I220" s="19"/>
       <c r="J220" s="20"/>
     </row>
-    <row r="221" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="221" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B221" s="15" t="s">
         <v>8</v>
       </c>
@@ -5952,7 +5952,7 @@
       <c r="I221" s="19"/>
       <c r="J221" s="20"/>
     </row>
-    <row r="222" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="222" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B222" s="15" t="s">
         <v>8</v>
       </c>
@@ -5975,7 +5975,7 @@
       <c r="I222" s="19"/>
       <c r="J222" s="20"/>
     </row>
-    <row r="223" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="223" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B223" s="15" t="s">
         <v>8</v>
       </c>
@@ -5998,7 +5998,7 @@
       <c r="I223" s="19"/>
       <c r="J223" s="20"/>
     </row>
-    <row r="224" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="224" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B224" s="15" t="s">
         <v>8</v>
       </c>
@@ -6021,7 +6021,7 @@
       <c r="I224" s="19"/>
       <c r="J224" s="20"/>
     </row>
-    <row r="225" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="225" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B225" s="15" t="s">
         <v>8</v>
       </c>
@@ -6044,7 +6044,7 @@
       <c r="I225" s="19"/>
       <c r="J225" s="20"/>
     </row>
-    <row r="226" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="226" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B226" s="15" t="s">
         <v>8</v>
       </c>
@@ -6067,7 +6067,7 @@
       <c r="I226" s="19"/>
       <c r="J226" s="20"/>
     </row>
-    <row r="227" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="227" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B227" s="15" t="s">
         <v>8</v>
       </c>
@@ -6090,7 +6090,7 @@
       <c r="I227" s="19"/>
       <c r="J227" s="20"/>
     </row>
-    <row r="228" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="228" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B228" s="15" t="s">
         <v>8</v>
       </c>
@@ -6113,7 +6113,7 @@
       <c r="I228" s="19"/>
       <c r="J228" s="20"/>
     </row>
-    <row r="229" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="229" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B229" s="15" t="s">
         <v>8</v>
       </c>
@@ -6136,7 +6136,7 @@
       <c r="I229" s="19"/>
       <c r="J229" s="20"/>
     </row>
-    <row r="230" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="230" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B230" s="15" t="s">
         <v>8</v>
       </c>
@@ -6159,7 +6159,7 @@
       <c r="I230" s="19"/>
       <c r="J230" s="20"/>
     </row>
-    <row r="231" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="231" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B231" s="15" t="s">
         <v>8</v>
       </c>
@@ -6182,7 +6182,7 @@
       <c r="I231" s="19"/>
       <c r="J231" s="20"/>
     </row>
-    <row r="232" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="232" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B232" s="15" t="s">
         <v>8</v>
       </c>
@@ -6205,7 +6205,7 @@
       <c r="I232" s="19"/>
       <c r="J232" s="20"/>
     </row>
-    <row r="233" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="233" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B233" s="15" t="s">
         <v>8</v>
       </c>
@@ -6228,7 +6228,7 @@
       <c r="I233" s="19"/>
       <c r="J233" s="20"/>
     </row>
-    <row r="234" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="234" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B234" s="15" t="s">
         <v>8</v>
       </c>
@@ -6251,7 +6251,7 @@
       <c r="I234" s="19"/>
       <c r="J234" s="20"/>
     </row>
-    <row r="235" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="235" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B235" s="15" t="s">
         <v>8</v>
       </c>
@@ -6274,7 +6274,7 @@
       <c r="I235" s="19"/>
       <c r="J235" s="20"/>
     </row>
-    <row r="236" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="236" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B236" s="15" t="s">
         <v>8</v>
       </c>
@@ -6297,7 +6297,7 @@
       <c r="I236" s="19"/>
       <c r="J236" s="20"/>
     </row>
-    <row r="237" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="237" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B237" s="15" t="s">
         <v>8</v>
       </c>
@@ -6320,7 +6320,7 @@
       <c r="I237" s="19"/>
       <c r="J237" s="20"/>
     </row>
-    <row r="238" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="238" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B238" s="15" t="s">
         <v>8</v>
       </c>
@@ -6343,7 +6343,7 @@
       <c r="I238" s="19"/>
       <c r="J238" s="20"/>
     </row>
-    <row r="239" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="239" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B239" s="15" t="s">
         <v>8</v>
       </c>
@@ -6366,7 +6366,7 @@
       <c r="I239" s="19"/>
       <c r="J239" s="20"/>
     </row>
-    <row r="240" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="240" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B240" s="15" t="s">
         <v>8</v>
       </c>
@@ -6389,7 +6389,7 @@
       <c r="I240" s="19"/>
       <c r="J240" s="20"/>
     </row>
-    <row r="241" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="241" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B241" s="15" t="s">
         <v>8</v>
       </c>
@@ -6412,7 +6412,7 @@
       <c r="I241" s="19"/>
       <c r="J241" s="20"/>
     </row>
-    <row r="242" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="242" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B242" s="15" t="s">
         <v>8</v>
       </c>
@@ -6435,7 +6435,7 @@
       <c r="I242" s="19"/>
       <c r="J242" s="20"/>
     </row>
-    <row r="243" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="243" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B243" s="15" t="s">
         <v>8</v>
       </c>
@@ -6458,7 +6458,7 @@
       <c r="I243" s="19"/>
       <c r="J243" s="20"/>
     </row>
-    <row r="244" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="244" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B244" s="15" t="s">
         <v>8</v>
       </c>
@@ -6481,7 +6481,7 @@
       <c r="I244" s="19"/>
       <c r="J244" s="20"/>
     </row>
-    <row r="245" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="245" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B245" s="15" t="s">
         <v>8</v>
       </c>
@@ -6504,7 +6504,7 @@
       <c r="I245" s="19"/>
       <c r="J245" s="20"/>
     </row>
-    <row r="246" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="246" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B246" s="15" t="s">
         <v>8</v>
       </c>
@@ -6527,7 +6527,7 @@
       <c r="I246" s="19"/>
       <c r="J246" s="20"/>
     </row>
-    <row r="247" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="247" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B247" s="15" t="s">
         <v>8</v>
       </c>
@@ -6550,7 +6550,7 @@
       <c r="I247" s="19"/>
       <c r="J247" s="20"/>
     </row>
-    <row r="248" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="248" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B248" s="15" t="s">
         <v>8</v>
       </c>
@@ -6573,7 +6573,7 @@
       <c r="I248" s="19"/>
       <c r="J248" s="20"/>
     </row>
-    <row r="249" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="249" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B249" s="15" t="s">
         <v>8</v>
       </c>
@@ -6596,7 +6596,7 @@
       <c r="I249" s="19"/>
       <c r="J249" s="20"/>
     </row>
-    <row r="250" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="250" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B250" s="15" t="s">
         <v>8</v>
       </c>
@@ -6619,7 +6619,7 @@
       <c r="I250" s="19"/>
       <c r="J250" s="20"/>
     </row>
-    <row r="251" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="251" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B251" s="15" t="s">
         <v>8</v>
       </c>
@@ -6642,7 +6642,7 @@
       <c r="I251" s="19"/>
       <c r="J251" s="20"/>
     </row>
-    <row r="252" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="252" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B252" s="15" t="s">
         <v>8</v>
       </c>
@@ -6665,7 +6665,7 @@
       <c r="I252" s="19"/>
       <c r="J252" s="20"/>
     </row>
-    <row r="253" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="253" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B253" s="15" t="s">
         <v>8</v>
       </c>
@@ -6688,7 +6688,7 @@
       <c r="I253" s="19"/>
       <c r="J253" s="20"/>
     </row>
-    <row r="254" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="254" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B254" s="15" t="s">
         <v>8</v>
       </c>
@@ -6711,7 +6711,7 @@
       <c r="I254" s="19"/>
       <c r="J254" s="20"/>
     </row>
-    <row r="255" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="255" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B255" s="15" t="s">
         <v>8</v>
       </c>
@@ -6734,7 +6734,7 @@
       <c r="I255" s="19"/>
       <c r="J255" s="20"/>
     </row>
-    <row r="256" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="256" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B256" s="15" t="s">
         <v>8</v>
       </c>
@@ -6757,7 +6757,7 @@
       <c r="I256" s="19"/>
       <c r="J256" s="20"/>
     </row>
-    <row r="257" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="257" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B257" s="15" t="s">
         <v>8</v>
       </c>
@@ -6780,7 +6780,7 @@
       <c r="I257" s="19"/>
       <c r="J257" s="20"/>
     </row>
-    <row r="258" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="258" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B258" s="15" t="s">
         <v>8</v>
       </c>
@@ -6803,7 +6803,7 @@
       <c r="I258" s="19"/>
       <c r="J258" s="20"/>
     </row>
-    <row r="259" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="259" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B259" s="15" t="s">
         <v>8</v>
       </c>
@@ -6826,7 +6826,7 @@
       <c r="I259" s="19"/>
       <c r="J259" s="20"/>
     </row>
-    <row r="260" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="260" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B260" s="15" t="s">
         <v>8</v>
       </c>
@@ -6849,7 +6849,7 @@
       <c r="I260" s="19"/>
       <c r="J260" s="20"/>
     </row>
-    <row r="261" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="261" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B261" s="15" t="s">
         <v>8</v>
       </c>
@@ -6872,7 +6872,7 @@
       <c r="I261" s="19"/>
       <c r="J261" s="20"/>
     </row>
-    <row r="262" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="262" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B262" s="15" t="s">
         <v>8</v>
       </c>
@@ -6895,7 +6895,7 @@
       <c r="I262" s="19"/>
       <c r="J262" s="20"/>
     </row>
-    <row r="263" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="263" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B263" s="15" t="s">
         <v>8</v>
       </c>
@@ -6918,7 +6918,7 @@
       <c r="I263" s="19"/>
       <c r="J263" s="20"/>
     </row>
-    <row r="264" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="264" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B264" s="15" t="s">
         <v>8</v>
       </c>
@@ -6941,7 +6941,7 @@
       <c r="I264" s="19"/>
       <c r="J264" s="20"/>
     </row>
-    <row r="265" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="265" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B265" s="15" t="s">
         <v>8</v>
       </c>
@@ -6964,7 +6964,7 @@
       <c r="I265" s="19"/>
       <c r="J265" s="20"/>
     </row>
-    <row r="266" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="266" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B266" s="15" t="s">
         <v>8</v>
       </c>
@@ -6987,7 +6987,7 @@
       <c r="I266" s="19"/>
       <c r="J266" s="20"/>
     </row>
-    <row r="267" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="267" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B267" s="15" t="s">
         <v>8</v>
       </c>
@@ -7010,7 +7010,7 @@
       <c r="I267" s="19"/>
       <c r="J267" s="20"/>
     </row>
-    <row r="268" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="268" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B268" s="15" t="s">
         <v>8</v>
       </c>
@@ -7033,7 +7033,7 @@
       <c r="I268" s="19"/>
       <c r="J268" s="20"/>
     </row>
-    <row r="269" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="269" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B269" s="15" t="s">
         <v>8</v>
       </c>
@@ -7056,7 +7056,7 @@
       <c r="I269" s="19"/>
       <c r="J269" s="20"/>
     </row>
-    <row r="270" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="270" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B270" s="15" t="s">
         <v>8</v>
       </c>
@@ -7079,7 +7079,7 @@
       <c r="I270" s="19"/>
       <c r="J270" s="20"/>
     </row>
-    <row r="271" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="271" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B271" s="15" t="s">
         <v>8</v>
       </c>
@@ -7102,7 +7102,7 @@
       <c r="I271" s="19"/>
       <c r="J271" s="20"/>
     </row>
-    <row r="272" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="272" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B272" s="15" t="s">
         <v>8</v>
       </c>
@@ -7125,7 +7125,7 @@
       <c r="I272" s="19"/>
       <c r="J272" s="20"/>
     </row>
-    <row r="273" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="273" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B273" s="15" t="s">
         <v>8</v>
       </c>
@@ -7148,7 +7148,7 @@
       <c r="I273" s="19"/>
       <c r="J273" s="20"/>
     </row>
-    <row r="274" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="274" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B274" s="15" t="s">
         <v>8</v>
       </c>
@@ -7171,7 +7171,7 @@
       <c r="I274" s="19"/>
       <c r="J274" s="20"/>
     </row>
-    <row r="275" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="275" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B275" s="15" t="s">
         <v>8</v>
       </c>
@@ -7194,7 +7194,7 @@
       <c r="I275" s="19"/>
       <c r="J275" s="20"/>
     </row>
-    <row r="276" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="276" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B276" s="15" t="s">
         <v>8</v>
       </c>
@@ -7217,7 +7217,7 @@
       <c r="I276" s="19"/>
       <c r="J276" s="20"/>
     </row>
-    <row r="277" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="277" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B277" s="15" t="s">
         <v>8</v>
       </c>
@@ -7240,7 +7240,7 @@
       <c r="I277" s="19"/>
       <c r="J277" s="20"/>
     </row>
-    <row r="278" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="278" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B278" s="15" t="s">
         <v>8</v>
       </c>
@@ -7263,7 +7263,7 @@
       <c r="I278" s="19"/>
       <c r="J278" s="20"/>
     </row>
-    <row r="279" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="279" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B279" s="15" t="s">
         <v>8</v>
       </c>
@@ -7286,7 +7286,7 @@
       <c r="I279" s="19"/>
       <c r="J279" s="20"/>
     </row>
-    <row r="280" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="280" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B280" s="15" t="s">
         <v>8</v>
       </c>
@@ -7309,7 +7309,7 @@
       <c r="I280" s="19"/>
       <c r="J280" s="20"/>
     </row>
-    <row r="281" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="281" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B281" s="15" t="s">
         <v>8</v>
       </c>
@@ -7332,7 +7332,7 @@
       <c r="I281" s="19"/>
       <c r="J281" s="20"/>
     </row>
-    <row r="282" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="282" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B282" s="15" t="s">
         <v>8</v>
       </c>
@@ -7355,7 +7355,7 @@
       <c r="I282" s="19"/>
       <c r="J282" s="20"/>
     </row>
-    <row r="283" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="283" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B283" s="21" t="s">
         <v>8</v>
       </c>
@@ -7378,7 +7378,7 @@
       <c r="I283" s="25"/>
       <c r="J283" s="26"/>
     </row>
-    <row r="288" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="288" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B288" s="32" t="s">
         <v>93</v>
       </c>
@@ -7389,7 +7389,7 @@
       <c r="I288" s="1"/>
       <c r="J288" s="1"/>
     </row>
-    <row r="289" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="289" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B289" s="32" t="s">
         <v>92</v>
       </c>
